--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 09/02. Trả bảo hành/TBH_GPSTayNinh_300926.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 09/02. Trả bảo hành/TBH_GPSTayNinh_300926.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 09\02. Trả bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC0C02C-7A11-4816-82AC-8F03152BEEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F8C59BC-E519-44EE-A0DD-D9C25FFDAA9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
